--- a/databases/teste_dunn_clusters_ans_inicio_kmeans3.xlsx
+++ b/databases/teste_dunn_clusters_ans_inicio_kmeans3.xlsx
@@ -399,12 +399,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1: lowest unsafe abortion rates</t>
+          <t>1: lowest induced abortion rates</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2: intermediary unsafe abortion rates</t>
+          <t>2: intermediary induced abortion rates</t>
         </is>
       </c>
       <c r="D2">
@@ -430,12 +430,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1: lowest unsafe abortion rates</t>
+          <t>1: lowest induced abortion rates</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3: highest unsafe abortion rates</t>
+          <t>3: highest induced abortion rates</t>
         </is>
       </c>
       <c r="D3">
@@ -461,12 +461,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2: intermediary unsafe abortion rates</t>
+          <t>2: intermediary induced abortion rates</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3: highest unsafe abortion rates</t>
+          <t>3: highest induced abortion rates</t>
         </is>
       </c>
       <c r="D4">
